--- a/sun-yuchen-course/files/kaiying-action-table.xlsx
+++ b/sun-yuchen-course/files/kaiying-action-table.xlsx
@@ -9,8 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="黎凯迎_大厂AIPM路线" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="黎凯迎_加入初创路线" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21天产出总览" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21天产出总览" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -485,7 +484,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>这是《孙宇晨155期访谈：21天商业开窍课》的学习行动表双人版。它不是普通打卡表，而是把21天课程转成你和赵仁杰/AuraCosmic团队各自能执行、能验证、能复盘的动作。</t>
+          <t>这是《孙宇晨155期访谈：21天商业开窍课》的个人学习行动表。它不是普通打卡表，而是把21天课程转成你在大厂AIPM路线中能执行、能验证、能复盘的动作。</t>
         </is>
       </c>
     </row>
@@ -502,11 +501,7 @@
       </c>
     </row>
     <row r="4" ht="58" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>你的初创团队路线</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="n"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>用于判断你是否加入赵仁杰团队，以及加入前后如何低风险证明价值。重点是角色定位、风险边界、30天试合作。</t>
@@ -514,16 +509,8 @@
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>赵仁杰_Aura路线</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>用于创始人和团队视角推进AuraCosmic的增长、商业化、ToB/ToC验证、线下体验闭环和复盘机制。</t>
-        </is>
-      </c>
+      <c r="A5" s="3" t="n"/>
+      <c r="B5" s="3" t="n"/>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -531,11 +518,7 @@
           <t>信息边界</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>赵仁杰个人资料仅使用你提供的信息，并以公开可核验方向作谨慎补充；Aura运营数据按你提供的内部信息处理：国内用户8000+、海外用户3000+、目前主要ToB收入，未来探索ToC。</t>
-        </is>
-      </c>
+      <c r="B6" s="2" t="n"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -545,7 +528,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>先学当天PPT/讲稿，再填写对应路线表。每一天至少留下一个输出物；没有输出物，就等于没有完成学习。</t>
+          <t>先学当天PPT/讲稿，再填写大厂AIPM路线表。每一天至少留下一个输出物；没有输出物，就等于没有完成学习。</t>
         </is>
       </c>
     </row>
@@ -771,7 +754,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>目标是大厂AIPM，但也有加入初创的可能。</t>
+          <t>目标是大厂AIPM，需要把学习内容转成可展示、可验证的岗位能力证据。</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1261,7 +1244,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>大厂路线和创业路线各自的不可逆风险是什么？</t>
+          <t>大厂AIPM路线里有哪些不可逆风险？</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -1271,7 +1254,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>列两条路线的机会成本、时间成本、声誉风险、学习风险。</t>
+          <t>列大厂AIPM路线的机会成本、时间成本、声誉风险、学习风险。</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -1281,7 +1264,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>双路线风险边界表。</t>
+          <t>大厂AIPM路线风险边界表。</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -1596,7 +1579,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>你还不知道大厂更适合你，还是初创更能放大你。</t>
+          <t>你需要判断大厂AIPM路线中哪些岗位、团队和业务更能放大你。</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1621,7 +1604,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>作为两条路线决策依据。</t>
+          <t>作为大厂AIPM路线决策依据。</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1761,7 +1744,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>需要把学习落到大厂路线和初创路线的真实动作。</t>
+          <t>需要把学习落到大厂AIPM路线的真实动作。</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1806,1245 +1789,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="38" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="34" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Day</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>学习板块</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>核心问题</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>现实处境</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>今日输入</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>今日处理动作</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>今日输出物</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>能力/业务映射</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>资产沉淀</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>验证指标</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>复盘问题</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="118" customHeight="1">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>复杂样本学习</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>我加入强创始人团队时，如何不盲目崇拜也不低估机会？</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>赵仁杰履历强、团队信念强，Aura上线早期仍需验证。</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>拆赵仁杰的可学点、不可复制点、团队风险点。</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>把“人很强”拆成能力、资源、执行、判断、协作五项证据。</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>创始人样本拆解卡。</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>判断是否适合共事</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>为正式沟通准备问题清单。</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>是否能区分个人优秀和项目确定性。</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>我被吸引的是人、产品、机会，还是想加入强者叙事？</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="118" customHeight="1">
-      <c r="A3" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>学习资产化</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>我能给团队带去什么方法资产，而不是只做杂活？</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>你有AI资料处理、Agent构建、用户分析能力。</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>把自己做课程/Agent的流程改写成团队可用SOP。</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>选择一个场景：用户访谈分析、活动复盘、商业化实验。</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>Aura PM/FDE工作流提案。</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>团队方法沉淀</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>加入团队后的首个贡献物。</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>团队是否能直接使用。</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>我能否在一周内证明价值？</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="118" customHeight="1">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>默认路径诊断</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>加入初创是不是逃离求职焦虑，还是主动战略选择？</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>你有大厂路线和创业路线两个选项。</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>写出加入团队的真实动机和担忧。</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>区分成长、收入、身份、关系、影响力、长期机会。</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>创业动机诊断表。</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>职业决策</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>用于和赵仁杰谈职责/预期。</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>是否识别出非理性动机。</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>如果团队暂时不赚钱，我还愿意做什么？</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="118" customHeight="1">
-      <c r="A5" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>选择权</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>加入Aura会扩大还是缩小我的选择权？</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>早期团队给高参与度，但也可能消耗时间。</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>列加入后可能获得的作品、数据、身份、股权、行业理解。</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>列失去的实习窗口、现金流、时间稳定性。</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>创业选择权评估。</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>机会成本判断</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>形成加入前谈判清单。</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>是否明确3个月后应获得什么。</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>这个选择是否让我未来更自由？</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="118" customHeight="1">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>个人战略</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>如果加入，我在团队里应该定位成什么？</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>团队已有PM和海外成员，你需要找到独特切入。</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>梳理团队现有角色和空缺。</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>定义你的位置：AI增长/用户研究/活动产品化/数据复盘/FDE。</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>加入Aura的角色定位一页纸。</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>角色设计；边界管理</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>发给团队讨论职责。</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>是否避免和现有PM重复。</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>我最不可替代的贡献是什么？</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="118" customHeight="1">
-      <c r="A7" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>价值观筛选器</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>什么样的团队合作我能长期投入？</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>团队相信产品能赚大钱，但你需要看机制。</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>列团队合作底线：数据透明、决策机制、权益、节奏、尊重。</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>设计加入前必须问清的10个问题。</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>团队合作筛选器。</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>合作判断</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>用于谈判前准备。</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>是否覆盖钱、权、责、退出。</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>我有没有不好意思问关键问题？</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="118" customHeight="1">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>个人主权</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>在朋友团队里如何既支持又保持判断？</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>朋友关系会让商业判断更难开口。</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>写出三类沟通：支持、质疑、拒绝。</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>准备“有证据的反对意见”表达模板。</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>朋友创业沟通边界。</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>协作沟通</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>降低朋友合作内耗。</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>是否能提出不伤关系的质疑。</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>我会不会因为关系而承担不清楚的责任？</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="118" customHeight="1">
-      <c r="A9" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>机会窗口</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>AI dating/线下社交现在是不是窗口？</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Aura已有国内8000+、海外3000+，且有线下合作。</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>拆窗口：AI匹配、年轻人社交疲惫、线下体验回归、商户获客。</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>判断窗口证据与反证。</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>Aura机会窗口地图。</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>行业判断</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>用于商业计划和路演叙事。</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>是否找到可验证的窗口信号。</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>这个窗口是真需求，还是概念叠加？</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="118" customHeight="1">
-      <c r="A10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>赛道判断</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Aura到底属于什么赛道、卖什么、卖给谁？</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>目前收入主要ToB，未来可能ToC。</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>拆标签：AI社交、dating、线下体验、商户获客、会员服务。</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>画用户、付费方、供给方、场景方四方关系。</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Aura赛道定位表。</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>商业定位</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>作为加入后第一份产品定位文档。</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>是否一句话讲清产品。</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>ToB和ToC是否互相增强？</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="118" customHeight="1">
-      <c r="A11" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>投资自己</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>加入前我最该补什么能力？</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>你需要从个人AI PM转向真实增长/商业化。</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>补3类能力：增长指标、社交产品机制、线下活动运营。</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>每天看一个竞品/一次用户访谈/一个商户案例。</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>加入前能力补齐表。</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>创业PM能力</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>为30天试用期准备。</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>是否能和团队业务直接挂钩。</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>我缺的不是热情，而是哪项硬能力？</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="118" customHeight="1">
-      <c r="A12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>杠杆</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>我能为Aura设计什么增长杠杆？</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>产品有用户、商户、活动三个杠杆点。</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>列AI匹配、用户内容、商户合作、校园社群、活动SOP。</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>选择两个最低成本杠杆做实验。</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Aura增长杠杆地图。</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>增长设计</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>转成MVP实验池。</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>是否有低成本高反馈动作。</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>哪个杠杆能最快带来真实数据？</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="118" customHeight="1">
-      <c r="A13" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>风险边界</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>我加入前必须确认哪些红线？</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>上线两周不赚钱正常，但权益和职责不能模糊。</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>准备股权/薪资/时间/职责/数据权限/退出机制问题。</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>设定3个月试运行边界。</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>加入前风险边界清单。</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>风险控制</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>和赵仁杰正式沟通。</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>是否把敏感问题问清楚。</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>如果答案含糊，我是否仍要加入？</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="118" customHeight="1">
-      <c r="A14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>原始积累</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>我如何把早期创业经历变成未来资产？</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>即使最后不加入，也能积累案例。</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>设计记录模板：假设、动作、数据、反馈、复盘。</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>每周沉淀一个商业化/增长案例。</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Aura实战资产库模板。</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>案例沉淀</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>服务未来面试和作品集。</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>每周是否有可展示产出。</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>我有没有把辛苦做事变成可证明资产？</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="118" customHeight="1">
-      <c r="A15" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>组合优势</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>我和团队现有成员如何互补？</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>团队已有强金融创始人、Kimi PM、海外成员。</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>列四个人的能力/资源/短板/可互补处。</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>找到你最适合补位的3个模块。</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>团队组合优势图。</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>团队协作</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>帮助团队分工。</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>是否减少角色重叠。</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>我加入后让团队多了什么，而不是多一个人？</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="118" customHeight="1">
-      <c r="A16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>表达与叙事</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Aura如何讲给用户、商户、投资人听？</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>目前需要把产品定位讲清。</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>分别写用户版、商户版、评委/投资人版一句话。</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>把“AI dating”改写成真实痛点叙事。</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>三套Aura叙事脚本。</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>产品叙事；商业表达</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>用于官网、路演、BD话术。</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>不同对象是否听到自己的利益。</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>我们是在讲概念，还是讲对方的问题？</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="118" customHeight="1">
-      <c r="A17" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>关系资产</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>线下合作如何从一次活动变成城市网络？</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>已有北京咖啡馆、酒吧、剧本杀合作。</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>列合作商户类型、诉求、付费理由、复购条件。</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>设计商户CRM字段和复盘机制。</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>商户关系资产表。</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>ToB运营</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>帮助ToB收入稳定化。</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>每个商户是否有ROI记录。</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>合作是资源堆积，还是网络资产？</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="118" customHeight="1">
-      <c r="A18" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>把自己当产品</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>我加入Aura后对团队的价值承诺是什么？</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>你需要让团队知道为什么需要你。</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>定义你的内部用户：创始人、PM、运营、商户、用户。</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>写价值承诺：把模糊增长问题拆成AI辅助实验和复盘闭环。</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>我的Aura价值承诺。</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>内部产品化</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>加入沟通材料。</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>是否有首月可交付清单。</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>团队为什么现在需要我？</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="118" customHeight="1">
-      <c r="A19" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>关键假设</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Aura最该验证的3个假设是什么？</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>ToB已有收入，ToC计划需要验证。</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>写假设：用户愿付费、线下提升信任、商户愿为到店付费。</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>设计验证指标和最小实验。</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>Aura关键假设表。</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>商业验证</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>进入30天实验池。</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>假设是否可测量。</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>我们现在最危险的未验证假设是什么？</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="118" customHeight="1">
-      <c r="A20" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>我能为Aura设计一个两周ToC付费实验吗？</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>你的建议是后期逐渐ToC收费。</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>选择权益：优先匹配、线下活动票、AI约会报告、会员筛选。</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>设计价格、样本、入口、转化指标。</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>ToC付费MVP方案。</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>商业化实验</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>交给团队试跑。</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>是否能在两周内得到付费信号。</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>用户愿意为什么付钱，不愿意为什么付钱？</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="118" customHeight="1">
-      <c r="A21" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>反馈与复盘</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>如何判断这个团队值得继续投入？</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>需要用真实数据而不是热情判断。</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>每周复盘获客、激活、匹配、到场、付费、复购、商户满意。</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>设定继续/调整/退出信号。</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>3个月合作复盘表。</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>战略复盘</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>作为加入决策依据。</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>是否有量化和质化证据。</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>我是在验证机会，还是被惯性绑定？</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="118" customHeight="1">
-      <c r="A22" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>商业开窍行动书</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>我接下来30天如何验证是否加入？</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>你需要小步进入，而不是一次性押上全部。</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>整合前20天输出，制定30天低风险试合作。</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>明确每周交付、每周复盘、最终决策标准。</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>加入Aura前30天验证计划。</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>行动系统</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>和团队对齐试合作。</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>30天后能否做出更确定选择。</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>什么结果会让我坚定加入，什么结果会让我暂停？</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
